--- a/data/trans_camb/P5B_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P5B_R-Edad-trans_camb.xlsx
@@ -624,12 +624,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-1,62</t>
+          <t>-1,61</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-1,12</t>
+          <t>-1,11</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,9</t>
+          <t>-0,89</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 1,06</t>
+          <t>-5,78; 1,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 2,09</t>
+          <t>-5,44; 1,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 6,41</t>
+          <t>-3,51; 5,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 1,91</t>
+          <t>-4,09; 2,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 1,62</t>
+          <t>-4,67; 1,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 3,38</t>
+          <t>-3,74; 3,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 0,89</t>
+          <t>-4,04; 0,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 0,74</t>
+          <t>-3,94; 0,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 3,55</t>
+          <t>-2,42; 3,31</t>
         </is>
       </c>
     </row>
@@ -730,12 +730,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-60,4%</t>
+          <t>-60,12%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-41,65%</t>
+          <t>-41,34%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-39,38%</t>
+          <t>-38,97%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>-50,25%</t>
+          <t>-49,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-51,7%</t>
+          <t>-51,57%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -793,37 +793,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 768,33</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-90,5; 140,04</t>
+          <t>-92,74; 142,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-91,36; 105,6</t>
+          <t>-93,2; 103,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-71,2; 322,24</t>
+          <t>-73,54; 288,85</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-0,6</t>
+          <t>-0,58</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,89</t>
+          <t>-1,88</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-1,91</t>
+          <t>-1,9</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 2,88</t>
+          <t>-3,38; 2,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 2,13</t>
+          <t>-3,27; 1,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 0,19</t>
+          <t>-4,7; 0,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 0,67</t>
+          <t>-5,07; 0,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,03; -0,49</t>
+          <t>-5,92; -0,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 1,39</t>
+          <t>-5,04; 1,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 0,68</t>
+          <t>-3,45; 0,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,83; -0,21</t>
+          <t>-3,8; -0,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,86; -0,03</t>
+          <t>-3,79; 0,17</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-20,51%</t>
+          <t>-19,86%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-70,79%</t>
+          <t>-70,69%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-43,79%</t>
+          <t>-43,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-52,7%</t>
+          <t>-52,45%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-52,57%</t>
+          <t>-52,47%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-71,47; 214,04</t>
+          <t>-79,92; 185,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-74,94; 160,34</t>
+          <t>-79,24; 145,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 83,79</t>
+          <t>-100,0; 56,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-83,47; 40,28</t>
+          <t>-84,44; 34,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-93,93; 2,05</t>
+          <t>-93,37; -11,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-84,74; 66,95</t>
+          <t>-83,02; 70,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-72,6; 30,49</t>
+          <t>-71,07; 33,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-81,39; -3,7</t>
+          <t>-80,83; 1,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-82,34; 9,25</t>
+          <t>-80,55; 22,54</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-2,96</t>
+          <t>-2,95</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,4; -0,91</t>
+          <t>-9,48; -1,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 1,28</t>
+          <t>-8,11; 0,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,48; -2,25</t>
+          <t>-10,16; -2,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 1,29</t>
+          <t>-2,74; 1,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 1,79</t>
+          <t>-2,26; 1,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 0,44</t>
+          <t>-3,2; 0,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,85; -0,37</t>
+          <t>-4,9; -0,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 0,89</t>
+          <t>-3,96; 0,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,56; -1,12</t>
+          <t>-5,24; -1,09</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-55,23%</t>
+          <t>-55,03%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-44,02%</t>
+          <t>-43,62%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1187,22 +1187,22 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-62,29%</t>
+          <t>-62,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>-78,06%</t>
+          <t>-77,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-43,15%</t>
+          <t>-43,02%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-92,31%</t>
+          <t>-92,29%</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 92,04</t>
+          <t>-100,0; 121,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-87,79; 93,62</t>
+          <t>-90,89; 45,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 24,97</t>
+          <t>-100,0; 6,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-81,79; 73,75</t>
+          <t>-81,73; 53,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -13,01</t>
+          <t>-100,0; -38,99</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-1,55</t>
+          <t>-1,53</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,36</t>
+          <t>5,38</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,43</t>
+          <t>1,44</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 2,44</t>
+          <t>-5,3; 2,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,31; -1,3</t>
+          <t>-7,58; -1,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 32,83</t>
+          <t>-5,13; 32,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 1,03</t>
+          <t>-4,37; 1,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 0,74</t>
+          <t>-4,69; 0,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 0,26</t>
+          <t>-5,14; -0,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 0,79</t>
+          <t>-3,95; 0,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,06; -1,0</t>
+          <t>-5,02; -1,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 20,41</t>
+          <t>-3,65; 17,96</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-33,05%</t>
+          <t>-32,76%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>114,55%</t>
+          <t>115,14%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>-42,43%</t>
+          <t>-42,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,92%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-83,44; 125,16</t>
+          <t>-80,34; 105,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -7,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1879,63</t>
+          <t>-100,0; 1546,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-93,46; 164,48</t>
+          <t>-100,0; 200,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 152,23</t>
+          <t>-100,0; 181,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-91,18; 59,67</t>
+          <t>-92,18; 39,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-78,25; 40,11</t>
+          <t>-76,09; 31,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-94,7; -20,69</t>
+          <t>-94,5; -29,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-86,93; 883,26</t>
+          <t>-86,48; 698,77</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-1,81</t>
+          <t>-1,8</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-2,05</t>
+          <t>-2,04</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>-0,53</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,68; -0,12</t>
+          <t>-3,47; -0,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,69; -0,43</t>
+          <t>-3,73; -0,54</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 14,71</t>
+          <t>-3,65; 12,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,82; -0,01</t>
+          <t>-2,95; -0,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,36; -0,54</t>
+          <t>-3,24; -0,59</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,15; -0,42</t>
+          <t>-3,22; -0,36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,77; -0,65</t>
+          <t>-2,87; -0,58</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,07; -0,95</t>
+          <t>-3,13; -0,97</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 5,83</t>
+          <t>-2,72; 5,66</t>
         </is>
       </c>
     </row>
@@ -1594,47 +1594,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-47,24%</t>
+          <t>-47,1%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-53,49%</t>
+          <t>-53,28%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-48,55%</t>
+          <t>-48,41%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-63,38%</t>
+          <t>-63,33%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-57,55%</t>
+          <t>-57,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>-48,08%</t>
+          <t>-47,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>-58,14%</t>
+          <t>-58,02%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-15,78%</t>
+          <t>-15,64%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-73,01; -0,95</t>
+          <t>-72,84; -1,56</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-77,0; -14,11</t>
+          <t>-75,13; -14,4</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-87,54; 464,95</t>
+          <t>-87,6; 498,65</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-75,32; 4,31</t>
+          <t>-75,89; -0,24</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-83,44; -16,93</t>
+          <t>-82,83; -22,11</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-79,09; -16,51</t>
+          <t>-79,43; -11,62</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-69,89; -21,84</t>
+          <t>-70,72; -19,61</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-74,46; -31,68</t>
+          <t>-75,54; -33,51</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-75,79; 194,8</t>
+          <t>-76,23; 183,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P5B_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P5B_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 1,06</t>
+          <t>-5,83; 1,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 1,77</t>
+          <t>-5,27; 2,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 5,95</t>
+          <t>-3,08; 6,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 2,06</t>
+          <t>-4,65; 1,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 1,61</t>
+          <t>-4,64; 0,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 3,56</t>
+          <t>-3,7; 3,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 0,68</t>
+          <t>-3,67; 0,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 0,61</t>
+          <t>-3,89; 0,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 3,31</t>
+          <t>-2,49; 3,54</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 768,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-92,74; 142,13</t>
+          <t>-90,2; 158,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-93,2; 103,98</t>
+          <t>-90,37; 132,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-73,54; 288,85</t>
+          <t>-71,86; 351,28</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 2,57</t>
+          <t>-3,06; 2,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 1,95</t>
+          <t>-3,27; 2,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 0,03</t>
+          <t>-4,57; 0,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 0,65</t>
+          <t>-4,97; 0,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,92; -0,74</t>
+          <t>-6,18; -0,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 1,32</t>
+          <t>-4,73; 1,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 0,66</t>
+          <t>-3,28; 0,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,8; -0,09</t>
+          <t>-3,98; -0,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 0,17</t>
+          <t>-4,02; 0,11</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-79,92; 185,7</t>
+          <t>-76,04; 153,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-79,24; 145,33</t>
+          <t>-77,3; 205,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 56,22</t>
+          <t>-100,0; 88,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-84,44; 34,64</t>
+          <t>-84,51; 33,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-93,37; -11,88</t>
+          <t>-94,04; -15,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-83,02; 70,9</t>
+          <t>-82,35; 67,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-71,07; 33,72</t>
+          <t>-69,66; 36,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-80,83; 1,94</t>
+          <t>-81,86; -0,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-80,55; 22,54</t>
+          <t>-82,73; 11,57</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,48; -1,31</t>
+          <t>-9,6; -1,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 0,65</t>
+          <t>-8,14; 0,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,16; -2,29</t>
+          <t>-10,36; -2,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 1,42</t>
+          <t>-2,97; 1,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 1,92</t>
+          <t>-2,86; 1,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 0,63</t>
+          <t>-3,5; 0,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,9; -0,48</t>
+          <t>-4,93; -0,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 0,78</t>
+          <t>-4,22; 0,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,24; -1,09</t>
+          <t>-5,34; -1,07</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 121,85</t>
+          <t>-100,0; -4,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-90,89; 45,7</t>
+          <t>-87,51; 58,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 6,03</t>
+          <t>-100,0; 7,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-81,73; 53,99</t>
+          <t>-86,14; 59,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -38,99</t>
+          <t>-100,0; 8,25</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 2,22</t>
+          <t>-5,41; 2,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,58; -1,59</t>
+          <t>-7,57; -1,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 32,14</t>
+          <t>-5,34; 33,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 1,17</t>
+          <t>-4,39; 1,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 0,82</t>
+          <t>-4,82; 0,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,14; -0,02</t>
+          <t>-4,97; 0,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 0,61</t>
+          <t>-3,94; 0,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,02; -1,24</t>
+          <t>-5,4; -1,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 17,96</t>
+          <t>-3,77; 17,0</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-80,34; 105,49</t>
+          <t>-81,2; 113,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 28,6</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 1974,88</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 136,36</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 1546,86</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 200,74</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 181,72</t>
-        </is>
-      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-92,18; 39,33</t>
+          <t>-91,4; 34,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-76,09; 31,36</t>
+          <t>-77,07; 34,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-94,5; -29,63</t>
+          <t>-95,66; -22,89</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-86,48; 698,77</t>
+          <t>-87,96; 569,09</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,47; -0,09</t>
+          <t>-3,46; -0,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,73; -0,54</t>
+          <t>-3,57; -0,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 12,78</t>
+          <t>-3,54; 14,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,95; -0,1</t>
+          <t>-2,91; -0,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,24; -0,59</t>
+          <t>-3,21; -0,59</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,22; -0,36</t>
+          <t>-3,05; -0,37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,87; -0,58</t>
+          <t>-2,78; -0,54</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,13; -0,97</t>
+          <t>-3,04; -0,89</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 5,66</t>
+          <t>-2,78; 7,16</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-72,84; -1,56</t>
+          <t>-74,47; -4,28</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-75,13; -14,4</t>
+          <t>-73,98; -10,43</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-87,6; 498,65</t>
+          <t>-86,94; 425,01</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-75,89; -0,24</t>
+          <t>-75,69; 2,51</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-82,83; -22,11</t>
+          <t>-83,15; -20,15</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-79,43; -11,62</t>
+          <t>-77,36; -13,2</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-70,72; -19,61</t>
+          <t>-68,26; -14,79</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-75,54; -33,51</t>
+          <t>-73,63; -29,8</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-76,23; 183,81</t>
+          <t>-75,77; 263,92</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P5B_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P5B_R-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,89</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,48</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-0,45</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-1,61</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-1,11</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,15</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,89</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,48</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,46</t>
+          <t>1,56</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,58</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 1,1</t>
+          <t>-4,62; 1,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 2,07</t>
+          <t>-4,58; 1,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 6,5</t>
+          <t>-3,81; 3,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 1,84</t>
+          <t>-5,97; 1,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 0,96</t>
+          <t>-5,49; 1,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 3,68</t>
+          <t>-3,11; 7,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 0,82</t>
+          <t>-4,05; 0,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 0,71</t>
+          <t>-4,04; 0,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 3,54</t>
+          <t>-2,15; 4,31</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-38,97%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-64,7%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-19,79%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-60,12%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-41,34%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>42,88%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-38,97%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-64,7%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-20,0%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-90,2; 158,85</t>
+          <t>-93,04; 97,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-90,37; 132,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-71,86; 351,28</t>
+          <t>-68,01; 375,13</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-2,13</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-3,05</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-1,55</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,27</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,58</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,01</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,13</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-3,05</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,88</t>
+          <t>-1,89</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,9</t>
+          <t>-1,69</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 2,43</t>
+          <t>-5,03; 0,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 2,29</t>
+          <t>-6,01; -0,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 0,15</t>
+          <t>-4,91; 1,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 0,64</t>
+          <t>-2,95; 2,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,18; -0,68</t>
+          <t>-3,67; 1,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 1,37</t>
+          <t>-4,47; 0,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 0,74</t>
+          <t>-3,32; 0,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,98; -0,13</t>
+          <t>-3,75; -0,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 0,11</t>
+          <t>-3,65; 0,26</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-49,33%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-70,69%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-35,84%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-9,3%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-19,86%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-69,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-49,33%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-70,69%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-43,57%</t>
+          <t>-64,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-52,47%</t>
+          <t>-46,71%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-76,04; 153,61</t>
+          <t>-83,47; 40,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-77,3; 205,55</t>
+          <t>-93,12; -12,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 88,33</t>
+          <t>-81,64; 96,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-84,51; 33,99</t>
+          <t>-71,47; 214,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-94,04; -15,18</t>
+          <t>-80,17; 140,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-82,35; 67,28</t>
+          <t>-100,0; 112,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-69,66; 36,66</t>
+          <t>-72,6; 30,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-81,86; -0,99</t>
+          <t>-78,0; 4,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-82,73; 11,57</t>
+          <t>-80,27; 14,53</t>
         </is>
       </c>
     </row>
@@ -1056,34 +1056,34 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,5</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,12</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-0,66</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-4,65</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-2,95</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>-5,36</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,5</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,12</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-0,71</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
           <t>-2,39</t>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,83</t>
+          <t>-2,81</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,6; -1,37</t>
+          <t>-2,76; 1,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 0,92</t>
+          <t>-2,5; 1,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,36; -2,2</t>
+          <t>-2,78; 0,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 1,29</t>
+          <t>-9,4; -0,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 1,61</t>
+          <t>-8,07; 0,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 0,62</t>
+          <t>-10,48; -2,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,93; -0,44</t>
+          <t>-5,0; -0,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 0,78</t>
+          <t>-3,88; 1,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,34; -1,07</t>
+          <t>-5,26; -1,12</t>
         </is>
       </c>
     </row>
@@ -1162,34 +1162,34 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-43,62%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-10,17%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-57,84%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-86,77%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-55,03%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-43,62%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-10,17%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-62,12%</t>
-        </is>
-      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>-77,98%</t>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-92,29%</t>
+          <t>-91,69%</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -4,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-87,51; 58,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 92,04</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>-90,52; 57,66</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 7,81</t>
+          <t>-100,0; 2,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-86,14; 59,8</t>
+          <t>-84,37; 66,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 8,25</t>
+          <t>-100,0; -22,75</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,63</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,94</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-2,05</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-1,53</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-4,14</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5,38</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,63</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,94</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,02</t>
+          <t>-3,29</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,44</t>
+          <t>-2,69</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 2,45</t>
+          <t>-4,73; 1,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,57; -1,59</t>
+          <t>-5,12; 0,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 33,12</t>
+          <t>-4,77; 0,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 1,15</t>
+          <t>-5,53; 2,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 0,58</t>
+          <t>-7,31; -1,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 0,09</t>
+          <t>-6,47; 1,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 0,76</t>
+          <t>-3,79; 0,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,4; -1,13</t>
+          <t>-5,06; -1,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 17,0</t>
+          <t>-4,89; -0,75</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-52,79%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-62,63%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-66,44%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-32,76%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-88,49%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>115,14%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-52,79%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-62,63%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-65,28%</t>
+          <t>-70,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>-69,17%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-81,2; 113,64</t>
+          <t>-93,46; 164,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 28,6</t>
+          <t>-100,0; 152,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1974,88</t>
+          <t>-91,12; 71,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 136,36</t>
+          <t>-85,87; 113,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; -7,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-91,4; 34,79</t>
+          <t>-100,0; 214,36</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-77,07; 34,38</t>
+          <t>-75,96; 34,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-95,66; -22,89</t>
+          <t>-94,7; -20,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-87,96; 569,09</t>
+          <t>-89,67; 2,13</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,46</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,91</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-1,69</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-1,8</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-2,04</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,87</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,46</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,91</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,73</t>
+          <t>-2,68</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,53</t>
+          <t>-2,17</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,46; -0,18</t>
+          <t>-3,08; 0,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,57; -0,4</t>
+          <t>-3,36; -0,73</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 14,19</t>
+          <t>-3,19; -0,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,91; -0,17</t>
+          <t>-3,67; -0,05</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,21; -0,59</t>
+          <t>-3,75; -0,44</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,05; -0,37</t>
+          <t>-4,25; -0,88</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,78; -0,54</t>
+          <t>-2,77; -0,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,04; -0,89</t>
+          <t>-3,07; -1,01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 7,16</t>
+          <t>-3,27; -1,13</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-48,41%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-63,33%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-56,03%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-47,1%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-53,28%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>22,77%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-48,41%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-63,33%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-57,46%</t>
+          <t>-69,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-15,64%</t>
+          <t>-63,56%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-74,47; -4,28</t>
+          <t>-76,73; 2,66</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-73,98; -10,43</t>
+          <t>-83,75; -24,98</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-86,94; 425,01</t>
+          <t>-79,71; -9,03</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-75,69; 2,51</t>
+          <t>-73,27; 4,52</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-83,15; -20,15</t>
+          <t>-75,39; -9,33</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-77,36; -13,2</t>
+          <t>-87,72; -19,45</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-68,26; -14,79</t>
+          <t>-67,48; -17,53</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-73,63; -29,8</t>
+          <t>-75,65; -31,37</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-75,77; 263,92</t>
+          <t>-79,2; -37,13</t>
         </is>
       </c>
     </row>
